--- a/workbooks/ru-age-specific-mortality-changes.xlsx
+++ b/workbooks/ru-age-specific-mortality-changes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8538A7-C880-42ED-AF71-062A21FDA7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282C0DB7-099E-4EA2-AEA4-973C17464D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{4B8C1302-2C97-4B88-98C8-E9F4E7BD81DC}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="17">
   <si>
     <t>Возрастные коэффициенты смертности qx для пола MALE</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>Infinity</t>
-  </si>
-  <si>
-    <t>Infinit</t>
   </si>
   <si>
     <t>Сокращённые возрастные коэффициенты смертности q0/mx для пола MALE</t>
@@ -104,9 +101,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -159,12 +157,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -174,6 +172,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -208,6 +210,56 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Смертность</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> детей в возрасте до года и 1-4 лет</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> (</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t>мужской пол ‰</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> q0 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t>и </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>m1-4)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -221,7 +273,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -252,7 +304,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -488,7 +540,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-73F4-4C21-A4EA-BA657281DD1C}"/>
+              <c16:uniqueId val="{00000000-FD92-4D72-8D62-34897E052077}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -501,7 +553,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>1-4</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -737,7 +789,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-73F4-4C21-A4EA-BA657281DD1C}"/>
+              <c16:uniqueId val="{00000001-FD92-4D72-8D62-34897E052077}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -749,8 +801,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1899479488"/>
-        <c:axId val="1899487648"/>
+        <c:axId val="5293184"/>
+        <c:axId val="5279264"/>
         <c:extLst>
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredScatterSeries>
@@ -769,7 +821,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>10</c:v>
+                        <c:v>5-14</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -1017,7 +1069,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000002-73F4-4C21-A4EA-BA657281DD1C}"/>
+                    <c16:uniqueId val="{00000002-FD92-4D72-8D62-34897E052077}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -1038,7 +1090,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>20</c:v>
+                        <c:v>15-24</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -1286,7 +1338,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000003-73F4-4C21-A4EA-BA657281DD1C}"/>
+                    <c16:uniqueId val="{00000003-FD92-4D72-8D62-34897E052077}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -1307,7 +1359,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>30</c:v>
+                        <c:v>25-34</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -1555,7 +1607,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000004-73F4-4C21-A4EA-BA657281DD1C}"/>
+                    <c16:uniqueId val="{00000004-FD92-4D72-8D62-34897E052077}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -1576,7 +1628,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>40</c:v>
+                        <c:v>35-44</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -1824,7 +1876,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000005-73F4-4C21-A4EA-BA657281DD1C}"/>
+                    <c16:uniqueId val="{00000005-FD92-4D72-8D62-34897E052077}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -1845,7 +1897,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>50</c:v>
+                        <c:v>45-54</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2099,7 +2151,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000006-73F4-4C21-A4EA-BA657281DD1C}"/>
+                    <c16:uniqueId val="{00000006-FD92-4D72-8D62-34897E052077}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -2120,7 +2172,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>62.5</c:v>
+                        <c:v>55-69</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -2374,7 +2426,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000007-73F4-4C21-A4EA-BA657281DD1C}"/>
+                    <c16:uniqueId val="{00000007-FD92-4D72-8D62-34897E052077}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -2383,9 +2435,11 @@
         </c:extLst>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1899479488"/>
+        <c:axId val="5293184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1990"/>
+          <c:min val="1870"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2425,7 +2479,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2440,14 +2494,16 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1899487648"/>
+        <c:crossAx val="5279264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1899487648"/>
+        <c:axId val="5279264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="350"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2465,7 +2521,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2487,7 +2543,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -2502,7 +2558,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1899479488"/>
+        <c:crossAx val="5293184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2529,7 +2585,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2576,7 +2632,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1800" b="1" i="0" baseline="0"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -2604,6 +2660,56 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr">
+              <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Смертность детей в возрасте 5-14 лет</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> (</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>мужской пол</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> ‰ mx</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.30412490985901514"/>
+          <c:y val="1.7499899472660511E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2616,8 +2722,8 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+          <a:pPr algn="ctr">
+            <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2648,7 +2754,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>5-14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2884,10 +2990,2215 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+              <c16:uniqueId val="{00000002-4874-4D89-A503-F6B458AF9F50}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="5293184"/>
+        <c:axId val="5279264"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$4:$AG$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>327.23</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>303.02999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>275.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>245.3</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>263.8</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>284.2</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>273.5</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>285.3</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>277.39999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>341.6</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>259.2</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>276.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>306.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>267.7</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>254</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>256.8</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>259.8</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>146.19999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>204</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>139.30000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>141.9</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>129.30000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>135.80000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>113.5</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>102.8</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>104.8</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>87.8</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>68.900000000000006</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>66.5</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>57.6</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>22.28</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>1-4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$5:$AG$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>70.550039999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>57.356099999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>51.674300000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>68.290729999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>61.489460000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>59.968150000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>66.064800000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>68.699510000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>66.756569999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>100.7838</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>73.757249999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>58.077950000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>72.355310000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>68.191720000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>65.239059999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>59.598520000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>59.353070000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>21.742000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>35.374099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>32.15795</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>17.612770000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>16.09132</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>16.399799999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>11.75337</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>10.14343</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>10.14165</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>8.0254499999999993</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>6.4192299999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>5.5125299999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>4.2115900000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.31107</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>15-24</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$7:$AG$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>7.6788800000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6.5498700000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>7.9075899999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.69984</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4.6993400000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5.7508600000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4.8991499999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7.2988</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8.1513299999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>31.948309999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>8.4499600000000008</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>5.4489099999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>5.3010299999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>7.2000799999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>7.4500500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>5.3513999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>4.5513899999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>4.3488899999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>5.04955</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>4.5481299999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>3.5998700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>3.2475499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>3.2505500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>2.9506199999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>2.8995099999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2.6998799999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2.4502000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2.2998099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2.3499099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2.2496299999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>8.6449300000000004</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>25-34</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$8:$AG$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>9.7555800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8.4062999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>9.6950000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>9.0007000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>7.2494199999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8.4993400000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6.9009299999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>9.5002499999999994</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>10.19909</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>35.650869999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>9.9999599999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>7.5489300000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>7.4986199999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10.45064</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>10.55067</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>7.4510399999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>6.0484499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>6.8004699999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>8.4480400000000007</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>7.0509300000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>5.7013299999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>5.24878</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>4.9513199999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>4.7000900000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>4.6508399999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>4.2992900000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>4.0000499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>3.9007000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>4.1999199999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>3.8003200000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>14.58719</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>35-44</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$9:$AG$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>14.339449999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>11.89364</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.1533</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>12.50094</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>10.35013</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>12.45041</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>10.300829999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>14.40114</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>15.649559999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>42.800669999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>14.80058</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12.801209999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13.0505</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>17.751380000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>17.95082</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>13.80105</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>11.85191</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>11.549160000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>14.602880000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>10.65255</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>8.7987500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>7.9503199999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>7.4987300000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>7.0506799999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>7.0505199999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>6.65076</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>6.1515700000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>6.0013899999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>6.3506</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>5.8495400000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>27.190999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="6"/>
+                <c:order val="6"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>45-54</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$10:$AG$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>23.801860000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>19.34816</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>22.034839999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>19.750910000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>16.50159</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>20.149989999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>17.050249999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>24.70252</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>27.20316</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>55.4026</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>25.452279999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>23.103120000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>23.652149999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>33.153280000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>33.153379999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>25.002839999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>21.552910000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>20.552499999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>27.901489999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>19.55172</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>16.701889999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>16.101050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>15.29974</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>14.85083</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>14.50131</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>13.901910000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>12.702019999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>12.201169999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>12.901289999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>11.549659999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>60.522370000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000006-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="7"/>
+                <c:order val="7"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>55-69</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$11:$AG$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>56.8307</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>41.784860000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>45.361719999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>43.507980000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>35.774700000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>43.21002</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>35.906469999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>51.213410000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>56.051879999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>84.0809</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>52.146439999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>47.012569999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>47.612430000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>68.188649999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>69.087900000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>53.880200000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>47.145069999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>42.57461</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>58.74691</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>40.17268</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>35.571109999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>35.505209999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>35.038670000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>35.238999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>35.806620000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>34.638979999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>32.871180000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>32.272060000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>34.672310000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30.872669999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>169.51866000000001</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000007-4874-4D89-A503-F6B458AF9F50}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="5293184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1990"/>
+          <c:min val="1870"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5279264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="5279264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="30"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5293184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1800" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Смертность</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> молодых мужчин (‰</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> mx)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="3"/>
           <c:order val="3"/>
@@ -2897,7 +5208,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>15-24</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3133,7 +5444,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+              <c16:uniqueId val="{00000003-E020-4CC9-9174-820F34EA79E9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3146,7 +5457,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>30</c:v>
+                  <c:v>25-34</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3382,7 +5693,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+              <c16:uniqueId val="{00000004-E020-4CC9-9174-820F34EA79E9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3395,7 +5706,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>35-44</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3631,10 +5942,1686 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+              <c16:uniqueId val="{00000005-E020-4CC9-9174-820F34EA79E9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="5293184"/>
+        <c:axId val="5279264"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$4:$AG$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>327.23</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>303.02999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>275.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>245.3</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>263.8</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>284.2</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>273.5</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>285.3</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>277.39999999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>341.6</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>259.2</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>276.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>306.60000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>267.7</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>254</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>256.8</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>259.8</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>146.19999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>204</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>139.30000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>141.9</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>129.30000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>135.80000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>113.5</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>102.8</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>104.8</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>87.8</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>68.900000000000006</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>66.5</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>57.6</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>22.28</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-E020-4CC9-9174-820F34EA79E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>1-4</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$5:$AG$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>70.550039999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>57.356099999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>51.674300000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>68.290729999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>61.489460000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>59.968150000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>66.064800000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>68.699510000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>66.756569999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>100.7838</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>73.757249999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>58.077950000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>72.355310000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>68.191720000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>65.239059999999995</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>59.598520000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>59.353070000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>21.742000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>35.374099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>32.15795</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>17.612770000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>16.09132</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>16.399799999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>11.75337</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>10.14343</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>10.14165</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>8.0254499999999993</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>6.4192299999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>5.5125299999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>4.2115900000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1.31107</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-E020-4CC9-9174-820F34EA79E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>5-14</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$6:$AG$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>11.49971</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>9.81921</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>8.0715800000000009</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>9.2068600000000007</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>7.8040099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>7.3530499999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7.90245</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7.9510300000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>7.6006200000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>29.853590000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7.3526100000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>7.8551599999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>8.1525800000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>6.6032099999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>5.9030199999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>4.6516700000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>5.0518900000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>3.5496099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>3.9505599999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>3.1504300000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>2.5985</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>2.2997700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>2.30077</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1.99909</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.8487800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.7505999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.5001800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1.4</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.34995</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1.2507999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>3.2360699999999998</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-E020-4CC9-9174-820F34EA79E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="6"/>
+                <c:order val="6"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>45-54</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$10:$AG$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>23.801860000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>19.34816</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>22.034839999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>19.750910000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>16.50159</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>20.149989999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>17.050249999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>24.70252</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>27.20316</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>55.4026</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>25.452279999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>23.103120000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>23.652149999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>33.153280000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>33.153379999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>25.002839999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>21.552910000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>20.552499999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>27.901489999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>19.55172</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>16.701889999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>16.101050000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>15.29974</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>14.85083</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>14.50131</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>13.901910000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>12.702019999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>12.201169999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>12.901289999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>11.549659999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>60.522370000000002</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000006-E020-4CC9-9174-820F34EA79E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="7"/>
+                <c:order val="7"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>55-69</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$11:$AG$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>56.8307</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>41.784860000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>45.361719999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>43.507980000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>35.774700000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>43.21002</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>35.906469999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>51.213410000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>56.051879999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>84.0809</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>52.146439999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>47.012569999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>47.612430000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>68.188649999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>69.087900000000005</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>53.880200000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>47.145069999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>42.57461</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>58.74691</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>40.17268</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>35.571109999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>35.505209999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>35.038670000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>35.238999999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>35.806620000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>34.638979999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>32.871180000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>32.272060000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>34.672310000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>30.872669999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>169.51866000000001</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000007-E020-4CC9-9174-820F34EA79E9}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+          </c:ext>
+        </c:extLst>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="5293184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1990"/>
+          <c:min val="1870"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5279264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="5279264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="45"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5293184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1800" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Смертность мужчин старших возрастов (‰</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> mx)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2160" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="6"/>
           <c:order val="6"/>
@@ -3644,7 +7631,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>50</c:v>
+                  <c:v>45-54</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3886,7 +7873,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+              <c16:uniqueId val="{00000006-5783-4961-B7DA-A56F46D848A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3899,7 +7886,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>62.5</c:v>
+                  <c:v>55-69</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4141,7 +8128,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+              <c16:uniqueId val="{00000007-5783-4961-B7DA-A56F46D848A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4153,8 +8140,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1899479488"/>
-        <c:axId val="1899487648"/>
+        <c:axId val="5293184"/>
+        <c:axId val="5279264"/>
         <c:extLst>
           <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
             <c15:filteredScatterSeries>
@@ -4173,7 +8160,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>0.5</c:v>
+                        <c:v>0</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -4421,7 +8408,7 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000000-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+                    <c16:uniqueId val="{00000000-5783-4961-B7DA-A56F46D848A4}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -4442,7 +8429,7 @@
                     <c:strCache>
                       <c:ptCount val="1"/>
                       <c:pt idx="0">
-                        <c:v>3</c:v>
+                        <c:v>1-4</c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -4690,7 +8677,1083 @@
                 <c:smooth val="1"/>
                 <c:extLst>
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-BEED-4EB4-AD0A-B9C1EC671ABE}"/>
+                    <c16:uniqueId val="{00000001-5783-4961-B7DA-A56F46D848A4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>5-14</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$6:$AG$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>11.49971</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>9.81921</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>8.0715800000000009</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>9.2068600000000007</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>7.8040099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>7.3530499999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7.90245</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7.9510300000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>7.6006200000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>29.853590000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>7.3526100000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>7.8551599999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>8.1525800000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>6.6032099999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>5.9030199999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>4.6516700000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>5.0518900000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>3.5496099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>3.9505599999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>3.1504300000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>2.5985</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>2.2997700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>2.30077</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1.99909</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1.8487800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1.7505999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1.5001800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1.4</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1.34995</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1.2507999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>3.2360699999999998</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-5783-4961-B7DA-A56F46D848A4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>15-24</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$7:$AG$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>7.6788800000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6.5498700000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>7.9075899999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>5.69984</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4.6993400000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5.7508600000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4.8991499999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7.2988</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8.1513299999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>31.948309999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>8.4499600000000008</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>5.4489099999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>5.3010299999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>7.2000799999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>7.4500500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>5.3513999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>4.5513899999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>4.3488899999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>5.04955</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>4.5481299999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>3.5998700000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>3.2475499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>3.2505500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>2.9506199999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>2.8995099999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>2.6998799999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>2.4502000000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>2.2998099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>2.3499099999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>2.2496299999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>8.6449300000000004</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-5783-4961-B7DA-A56F46D848A4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>25-34</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$8:$AG$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>9.7555800000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>8.4062999999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>9.6950000000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>9.0007000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>7.2494199999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8.4993400000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6.9009299999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>9.5002499999999994</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>10.19909</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>35.650869999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>9.9999599999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>7.5489300000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>7.4986199999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>10.45064</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>10.55067</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>7.4510399999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>6.0484499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>6.8004699999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>8.4480400000000007</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>7.0509300000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>5.7013299999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>5.24878</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>4.9513199999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>4.7000900000000003</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>4.6508399999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>4.2992900000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>4.0000499999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>3.9007000000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>4.1999199999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>3.8003200000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>14.58719</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-5783-4961-B7DA-A56F46D848A4}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredScatterSeries>
+            <c15:filteredScatterSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$B$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>35-44</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="19050" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:xVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$3:$AG$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>1879</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1897</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1908</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1927</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1928</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1929</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>1930</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>1931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>1932</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>1933</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>1934</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>1935</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>1936</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>1937</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>1938</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>1939</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>1940</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>1946</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>1947</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>1948</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>1949</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>1950</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>1951</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>1952</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>1953</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>1954</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>1955</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>1956</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>1957</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>1958</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>1987</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:xVal>
+                <c:yVal>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'M-q0mx-сокращ'!$C$9:$AG$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0.000</c:formatCode>
+                      <c:ptCount val="31"/>
+                      <c:pt idx="0">
+                        <c:v>14.339449999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>11.89364</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>14.1533</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>12.50094</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>10.35013</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>12.45041</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>10.300829999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>14.40114</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>15.649559999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>42.800669999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>14.80058</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>12.801209999999999</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>13.0505</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>17.751380000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>17.95082</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>13.80105</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>11.85191</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>11.549160000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>14.602880000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>10.65255</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>8.7987500000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>7.9503199999999996</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>7.4987300000000001</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>7.0506799999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>7.0505199999999997</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>6.65076</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>6.1515700000000004</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>6.0013899999999998</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>6.3506</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>5.8495400000000002</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>27.190999999999999</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:yVal>
+                <c:smooth val="1"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-5783-4961-B7DA-A56F46D848A4}"/>
                   </c:ext>
                 </c:extLst>
               </c15:ser>
@@ -4699,9 +9762,11 @@
         </c:extLst>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1899479488"/>
+        <c:axId val="5293184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1990"/>
+          <c:min val="1870"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -4741,7 +9806,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4756,14 +9821,16 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1899487648"/>
+        <c:crossAx val="5279264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1899487648"/>
+        <c:axId val="5279264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="170"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4781,7 +9848,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4803,7 +9870,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4818,9 +9885,10 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1899479488"/>
+        <c:crossAx val="5293184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -4845,7 +9913,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4892,7 +9960,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1800" b="1" i="0" baseline="0"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -4946,6 +10014,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6017,27 +11165,1059 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>504824</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>153352</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>27622</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>10476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96B01C1F-6ED0-97DC-7B96-44AC8B0A2357}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3712C38-FE10-F9B5-47BE-C8A879E08339}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6057,23 +12237,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1085850</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>180023</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>58103</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="7" name="Chart 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9E85F92-4F00-4530-960C-58004EC946EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFFC7562-40A0-42AD-9ADE-0107F88B7E0F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6088,6 +12268,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>608648</xdr:colOff>
+      <xdr:row>154</xdr:row>
+      <xdr:rowOff>20003</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB7635EB-974E-4F90-AFAD-023780624F51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>608648</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>20003</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{518E0C14-41DA-4405-8CD3-30D54C86E483}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -26425,7 +32681,7 @@
         <v>221.64467999999999</v>
       </c>
       <c r="AF104" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -26435,27 +32691,27 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5823C8A2-5186-4DE3-853C-6B8C7F7A3F64}">
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AP36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.41796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.3125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.3125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.41796875" bestFit="1" customWidth="1"/>
     <col min="3" max="28" width="7.20703125" bestFit="1" customWidth="1"/>
     <col min="29" max="32" width="6.20703125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7.20703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>5</v>
+    <row r="1" spans="1:37" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>1</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="7">
         <v>1879</v>
@@ -26550,13 +32806,14 @@
       <c r="AG3" s="7">
         <v>1987</v>
       </c>
+      <c r="AK3" s="1"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="9">
         <v>0.5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="3">
         <v>327.23</v>
@@ -26651,13 +32908,14 @@
       <c r="AG4" s="3">
         <v>22.28</v>
       </c>
+      <c r="AK4" s="1"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="9">
         <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C5" s="3">
         <v>70.550039999999996</v>
@@ -26752,13 +33010,14 @@
       <c r="AG5" s="3">
         <v>1.31107</v>
       </c>
+      <c r="AK5" s="1"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="9">
         <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C6" s="3">
         <v>11.49971</v>
@@ -26853,13 +33112,14 @@
       <c r="AG6" s="3">
         <v>3.2360699999999998</v>
       </c>
+      <c r="AK6" s="1"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="9">
         <v>20</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="C7" s="3">
         <v>7.6788800000000004</v>
@@ -26954,13 +33214,14 @@
       <c r="AG7" s="3">
         <v>8.6449300000000004</v>
       </c>
+      <c r="AK7" s="1"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="9">
         <v>30</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="C8" s="3">
         <v>9.7555800000000001</v>
@@ -27055,13 +33316,14 @@
       <c r="AG8" s="3">
         <v>14.58719</v>
       </c>
+      <c r="AK8" s="1"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="9">
         <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C9" s="3">
         <v>14.339449999999999</v>
@@ -27156,13 +33418,14 @@
       <c r="AG9" s="3">
         <v>27.190999999999999</v>
       </c>
+      <c r="AK9" s="1"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="9">
         <v>50</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="C10" s="3">
         <v>23.801860000000001</v>
@@ -27257,13 +33520,14 @@
       <c r="AG10" s="3">
         <v>60.522370000000002</v>
       </c>
+      <c r="AK10" s="1"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="9">
         <v>62.5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C11" s="3">
         <v>56.8307</v>
@@ -27358,6 +33622,16 @@
       <c r="AG11" s="3">
         <v>169.51866000000001</v>
       </c>
+      <c r="AK11" s="1"/>
+    </row>
+    <row r="33" spans="42:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="AP33" s="8"/>
+    </row>
+    <row r="34" spans="42:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="AP34" s="8"/>
+    </row>
+    <row r="36" spans="42:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="AP36" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27372,7 +33646,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.55000000000000004">
@@ -37383,7 +43657,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.55000000000000004">
@@ -47400,7 +53674,7 @@
   <sheetData>
     <row r="1" spans="1:33" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.55000000000000004">
@@ -47408,7 +53682,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="7">
         <v>1879</v>
@@ -47506,7 +53780,7 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4">
         <v>0.5</v>
@@ -47607,7 +53881,7 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>3</v>
@@ -47708,7 +53982,7 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4">
         <v>10</v>
@@ -47809,7 +54083,7 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="4">
         <v>20</v>
@@ -47910,7 +54184,7 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="4">
         <v>30</v>
@@ -48011,7 +54285,7 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="4">
         <v>40</v>
@@ -48112,7 +54386,7 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="4">
         <v>50</v>
@@ -48213,7 +54487,7 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="4">
         <v>62.5</v>
